--- a/docs/downloads/04/tbl_class_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_class_alaotra_ambodivoara.xlsx
@@ -440,14 +440,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>5.9</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -466,12 +460,6 @@
           <t>Primaire</t>
         </is>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>44.4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -489,12 +477,6 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>33.3</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,14 +491,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>22.2</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -578,14 +554,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>10</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -601,14 +571,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>75</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -624,14 +588,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>25</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -647,14 +605,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E13">
-        <v>8.300000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="14">
@@ -670,14 +628,8 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>22</v>
-      </c>
-      <c r="E14">
-        <v>91.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -739,14 +691,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>0.6</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -808,7 +754,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D20">
@@ -877,14 +823,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D23">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E23">
-        <v>17.4</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="24">
@@ -895,19 +841,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>1.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="25">
@@ -923,14 +869,8 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>21</v>
-      </c>
-      <c r="E25">
-        <v>53.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -946,14 +886,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>43.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="27">
@@ -964,19 +904,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3-5 ans</t>
+          <t>6-10 ans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>2.6</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -992,14 +926,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D28">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="E28">
-        <v>12.9</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="29">
@@ -1015,14 +949,8 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>185</v>
-      </c>
-      <c r="E29">
-        <v>85.3</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1038,14 +966,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E30">
-        <v>1.8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
